--- a/entregas/Expediente_Ramon_Acin_caja_0.xlsx
+++ b/entregas/Expediente_Ramon_Acin_caja_0.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>Año de expediente estimado: según su biografía ingresó en el Instituto de Segunda Enseñanza «a los doce años» (hacia 1900); compruébalo en el expediente original y corrígelo si hace falta. ILUSTRE: Ramón Arsenio Acín Aquilué (Huesca, 30-VIII-1888 – Huesca, 6-VIII-1936), pintor, escultor, periodista y pedagogo anarquista; profesor numerario de Dibujo de las Escuelas Normales de Huesca desde 1917; fundador de la revista «Floreal» (1919); financió con un premio de lotería la película «Las Hurdes, tierra sin pan» de Luis Buñuel (1933); autor de las «Pajaritas» del parque Miguel Servet de Huesca. Fusilado en las tapias del cementerio de Huesca al inicio de la Guerra Civil, días después que su esposa Concha Monrás. Hijo de Santos Acín Mulier y María Aquilué Royán; hermano de Santos Acín y Aguilué (caja 2). Fuentes: Real Academia de la Historia, https://historia-hispanica.rah.es/biografias/384 ; Wikipedia, https://es.wikipedia.org/wiki/Ram%C3%B3n_Ac%C3%ADn_Aquilu%C3%A9 ; Fundación Ramón y Katia Acín, https://fundacionacin.org/ramon-acin-aquilue/ . Expediente guardado aparte, con los de otros alumnos ilustres (caja 0).</t>
+          <t>Año de expediente estimado: según su biografía ingresó en el Instituto de Segunda Enseñanza «a los doce años» (hacia 1900); compruébalo en el expediente original y corrígelo si hace falta. ILUSTRE: Ramón Arsenio Acín Aquilué (Huesca, 30-VIII-1888 – Huesca, 6-VIII-1936), pintor, escultor, periodista y pedagogo anarquista; profesor numerario de Dibujo de las Escuelas Normales de Huesca desde 1917; fundador de la revista «Floreal» (1919); con parte del premio gordo de la lotería de Navidad financió la película de Luis Buñuel «Las Hurdes, tierra sin pan». Fusilado en la tapia del cementerio de Huesca al inicio de la Guerra Civil; su esposa, la pianista Concha Monrás, fue asesinada el 23-VIII-1936. Hijo de Santos Acín Mulier y María Aquilué Royán; hermano de Santos Acín y Aguilué (caja 2). Fuentes: Real Academia de la Historia, https://historia-hispanica.rah.es/biografias/384 ; Wikipedia, https://es.wikipedia.org/wiki/Ram%C3%B3n_Ac%C3%ADn_Aquilu%C3%A9 ; Fundación Ramón y Katia Acín, https://fundacionacin.org/ramon-acin-aquilue/ . Expediente guardado aparte, con los de otros alumnos ilustres (caja 0).</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
